--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1614-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1614-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB178A4E-9392-4F0B-949F-F80F5845BAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E78A3F6-F37E-4B51-B7E4-8BFBBE1B632A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{BD6142B9-7AB5-4DF6-AC8A-0129C427A836}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{676D37B8-E1C8-4C81-8038-A5EFC70835BF}"/>
   </bookViews>
   <sheets>
     <sheet name="1614-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1580,29 +1580,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9460F583-8EF8-4B07-B791-75894616954C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C367EF50-AC10-4E29-98EB-2F9CAC9EBBAC}">
   <dimension ref="A1:X41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="8" width="6.25" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1636,7 +1635,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1672,7 +1671,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1724,7 +1723,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1792,7 +1791,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1936,7 +1935,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2008,7 +2007,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2080,7 +2079,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2152,7 +2151,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2224,7 +2223,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2296,7 +2295,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2368,7 +2367,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2440,7 +2439,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2512,7 +2511,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2584,7 +2583,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2656,7 +2655,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2728,7 +2727,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2800,7 +2799,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2872,7 +2871,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2944,7 +2943,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -3016,7 +3015,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3088,7 +3087,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3160,7 +3159,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3232,7 +3231,7 @@
         <v>9.0399999999999991</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3304,7 +3303,7 @@
         <v>9.44</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2003</v>
       </c>
@@ -3376,7 +3375,7 @@
         <v>7.99</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2002</v>
       </c>
@@ -3448,7 +3447,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2001</v>
       </c>
@@ -3520,7 +3519,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2000</v>
       </c>
@@ -3592,7 +3591,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="41">
         <v>1999</v>
       </c>
@@ -3664,7 +3663,7 @@
         <v>8.2899999999999991</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="43"/>
       <c r="B31" s="44"/>
       <c r="C31" s="18" t="s">
@@ -3692,7 +3691,7 @@
       <c r="W31" s="50"/>
       <c r="X31" s="46"/>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1998</v>
       </c>
@@ -3764,7 +3763,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>1997</v>
       </c>
@@ -3836,7 +3835,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>1996</v>
       </c>
@@ -3908,7 +3907,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>1995</v>
       </c>
@@ -3980,7 +3979,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="51">
         <v>1994</v>
       </c>
@@ -4052,7 +4051,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="53"/>
       <c r="B37" s="54"/>
       <c r="C37" s="20" t="s">
@@ -4080,7 +4079,7 @@
       <c r="W37" s="60"/>
       <c r="X37" s="56"/>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="41">
         <v>1993</v>
       </c>
@@ -4152,7 +4151,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="43"/>
       <c r="B39" s="44"/>
       <c r="C39" s="18" t="s">
@@ -4180,7 +4179,7 @@
       <c r="W39" s="50"/>
       <c r="X39" s="46"/>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>1992</v>
       </c>
@@ -4252,7 +4251,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39" t="s">
         <v>62</v>
       </c>
